--- a/Results_experiment/exp_4/preds_1111144422222222.xlsx
+++ b/Results_experiment/exp_4/preds_1111144422222222.xlsx
@@ -924,7 +924,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D2">
-        <v>4.016545295715332</v>
+        <v>4.554300785064697</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -938,7 +938,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D3">
-        <v>2.53327465057373</v>
+        <v>1.846819043159485</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -952,7 +952,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D4">
-        <v>1.654743432998657</v>
+        <v>1.147778272628784</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -966,7 +966,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D5">
-        <v>0.8391828536987305</v>
+        <v>1.085067868232727</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -980,7 +980,7 @@
         <v>0.5</v>
       </c>
       <c r="D6">
-        <v>2.131030321121216</v>
+        <v>1.728080034255981</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -994,7 +994,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D7">
-        <v>2.898942708969116</v>
+        <v>2.716620445251465</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1008,7 +1008,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D8">
-        <v>0.8558114767074585</v>
+        <v>0.8166812062263489</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1022,7 +1022,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D9">
-        <v>3.570464849472046</v>
+        <v>3.411316871643066</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1036,7 +1036,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D10">
-        <v>0.8787572383880615</v>
+        <v>0.8504299521446228</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1050,7 +1050,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D11">
-        <v>2.097443103790283</v>
+        <v>2.014751434326172</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1064,7 +1064,7 @@
         <v>1.5</v>
       </c>
       <c r="D12">
-        <v>6.732354164123535</v>
+        <v>4.800026893615723</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1078,7 +1078,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D13">
-        <v>1.639360427856445</v>
+        <v>1.442929744720459</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1092,7 +1092,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D14">
-        <v>1.633170127868652</v>
+        <v>1.376317262649536</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D15">
-        <v>1.975841999053955</v>
+        <v>2.30291223526001</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1120,7 +1120,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D16">
-        <v>1.084576368331909</v>
+        <v>1.011138916015625</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D17">
-        <v>4.760288238525391</v>
+        <v>3.816479206085205</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1148,7 +1148,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D18">
-        <v>5.349308967590332</v>
+        <v>6.887717723846436</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1162,7 +1162,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D19">
-        <v>1.173187851905823</v>
+        <v>1.036792635917664</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1176,7 +1176,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D20">
-        <v>1.506577849388123</v>
+        <v>1.074303150177002</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D21">
-        <v>7.180233001708984</v>
+        <v>10.23723411560059</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1204,7 +1204,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D22">
-        <v>1.989561796188354</v>
+        <v>2.967080593109131</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1218,7 +1218,7 @@
         <v>0.5</v>
       </c>
       <c r="D23">
-        <v>2.878689050674438</v>
+        <v>3.309989452362061</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1232,7 +1232,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>2.525391101837158</v>
+        <v>1.187757015228271</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1246,7 +1246,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D25">
-        <v>1.78359043598175</v>
+        <v>1.552263975143433</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1260,7 +1260,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D26">
-        <v>1.85564661026001</v>
+        <v>1.129200577735901</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1274,7 +1274,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>0.8811585903167725</v>
+        <v>1.018025636672974</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1288,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>2.523739814758301</v>
+        <v>3.649475574493408</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1302,7 +1302,7 @@
         <v>5.5</v>
       </c>
       <c r="D29">
-        <v>3.531182289123535</v>
+        <v>3.021392345428467</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D30">
-        <v>0.9078198671340942</v>
+        <v>0.8407894968986511</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1330,7 +1330,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D31">
-        <v>3.774826049804688</v>
+        <v>3.565881252288818</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1344,7 +1344,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D32">
-        <v>1.244358897209167</v>
+        <v>1.098172187805176</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D33">
-        <v>0.8527510166168213</v>
+        <v>0.9238326549530029</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1372,7 +1372,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D34">
-        <v>3.088966608047485</v>
+        <v>3.325646877288818</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1386,7 +1386,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D35">
-        <v>3.63343071937561</v>
+        <v>3.433999538421631</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1400,7 +1400,7 @@
         <v>7.5</v>
       </c>
       <c r="D36">
-        <v>3.968286991119385</v>
+        <v>4.270342826843262</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1414,7 +1414,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D37">
-        <v>2.352090358734131</v>
+        <v>2.459447860717773</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>2.256705760955811</v>
+        <v>3.735202789306641</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1442,7 +1442,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D39">
-        <v>2.214436054229736</v>
+        <v>2.117941379547119</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1456,7 +1456,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D40">
-        <v>0.8845609426498413</v>
+        <v>1.124660134315491</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1470,7 +1470,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D41">
-        <v>1.758785724639893</v>
+        <v>4.155962467193604</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1484,7 +1484,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D42">
-        <v>1.940871000289917</v>
+        <v>1.309067726135254</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1498,7 +1498,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D43">
-        <v>3.139743089675903</v>
+        <v>3.497539043426514</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1512,7 +1512,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D44">
-        <v>5.731047630310059</v>
+        <v>7.836580276489258</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1526,7 +1526,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>1.506996393203735</v>
+        <v>1.226736307144165</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1540,7 +1540,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D46">
-        <v>2.193410158157349</v>
+        <v>1.481235980987549</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1554,7 +1554,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D47">
-        <v>6.034043312072754</v>
+        <v>3.77647066116333</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1568,7 +1568,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D48">
-        <v>2.108668327331543</v>
+        <v>1.83180844783783</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>1.765053868293762</v>
+        <v>1.258829236030579</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1596,7 +1596,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D50">
-        <v>3.886029005050659</v>
+        <v>3.763046741485596</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>3.407292127609253</v>
+        <v>3.349953174591064</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>23.29999923706055</v>
       </c>
       <c r="D52">
-        <v>16.57682991027832</v>
+        <v>15.10888004302979</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1638,7 +1638,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D53">
-        <v>1.403096318244934</v>
+        <v>0.9507964849472046</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>4.221379280090332</v>
+        <v>3.03391695022583</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1666,7 +1666,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D55">
-        <v>2.214670181274414</v>
+        <v>1.775975108146667</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1680,7 +1680,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D56">
-        <v>2.145323276519775</v>
+        <v>1.537060737609863</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1694,7 +1694,7 @@
         <v>2.5</v>
       </c>
       <c r="D57">
-        <v>1.160515666007996</v>
+        <v>1.155716419219971</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D58">
-        <v>4.996310234069824</v>
+        <v>5.797262191772461</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D59">
-        <v>3.831704139709473</v>
+        <v>4.056282997131348</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1736,7 +1736,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D60">
-        <v>1.44686484336853</v>
+        <v>1.266716241836548</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D61">
-        <v>1.493756651878357</v>
+        <v>1.750805377960205</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D62">
-        <v>1.382743954658508</v>
+        <v>1.091570258140564</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1778,7 +1778,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D63">
-        <v>3.518069982528687</v>
+        <v>3.624711990356445</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1792,7 +1792,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D64">
-        <v>0.8478187322616577</v>
+        <v>0.9354181289672852</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>1.264139890670776</v>
+        <v>1.135338425636292</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1820,7 +1820,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D66">
-        <v>3.508795261383057</v>
+        <v>2.21785831451416</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D67">
-        <v>3.435664415359497</v>
+        <v>3.18186616897583</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D68">
-        <v>0.8899408578872681</v>
+        <v>0.8385195732116699</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D69">
-        <v>7.881874084472656</v>
+        <v>9.432133674621582</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
       <c r="D70">
-        <v>2.80671238899231</v>
+        <v>2.523640871047974</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D71">
-        <v>2.39422607421875</v>
+        <v>2.526840209960938</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1904,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="D72">
-        <v>1.139697313308716</v>
+        <v>1.755320310592651</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1918,7 +1918,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D73">
-        <v>2.12514853477478</v>
+        <v>2.243236064910889</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D74">
-        <v>0.8652560114860535</v>
+        <v>0.8824371099472046</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D75">
-        <v>3.301841497421265</v>
+        <v>3.093358516693115</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1960,7 +1960,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D76">
-        <v>4.677558898925781</v>
+        <v>3.795355319976807</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1974,7 +1974,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D77">
-        <v>0.8631229400634766</v>
+        <v>0.8903577327728271</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1988,7 +1988,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>1.739184141159058</v>
+        <v>3.09415864944458</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>0.8074687123298645</v>
+        <v>2.28957724571228</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D80">
-        <v>1.123891830444336</v>
+        <v>0.9848368167877197</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2030,7 +2030,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D81">
-        <v>1.073962450027466</v>
+        <v>1.032349228858948</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2044,7 +2044,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D82">
-        <v>1.09887170791626</v>
+        <v>0.9853594303131104</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D83">
-        <v>0.9239985942840576</v>
+        <v>0.9066551327705383</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2072,7 +2072,7 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>6.490288734436035</v>
+        <v>7.901909828186035</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2086,7 +2086,7 @@
         <v>0.5</v>
       </c>
       <c r="D85">
-        <v>1.093364715576172</v>
+        <v>1.925462961196899</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D86">
-        <v>1.195337414741516</v>
+        <v>0.9984381198883057</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2114,7 +2114,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D87">
-        <v>2.468716144561768</v>
+        <v>2.595678329467773</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2128,7 +2128,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D88">
-        <v>2.214793920516968</v>
+        <v>2.477994918823242</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2142,7 +2142,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D89">
-        <v>2.861231565475464</v>
+        <v>3.326537132263184</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2156,7 +2156,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D90">
-        <v>4.133901596069336</v>
+        <v>4.583003520965576</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2170,7 +2170,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D91">
-        <v>5.343818664550781</v>
+        <v>5.687978744506836</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2184,7 +2184,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D92">
-        <v>1.259938597679138</v>
+        <v>4.182788372039795</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2198,7 +2198,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D93">
-        <v>1.478329181671143</v>
+        <v>1.120274066925049</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2212,7 +2212,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D94">
-        <v>1.33073103427887</v>
+        <v>1.063502311706543</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2226,7 +2226,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D95">
-        <v>0.8698467016220093</v>
+        <v>0.9228052496910095</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2240,7 +2240,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D96">
-        <v>1.030779600143433</v>
+        <v>0.8786866068840027</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2254,7 +2254,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D97">
-        <v>3.706925868988037</v>
+        <v>3.68548583984375</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2268,7 +2268,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D98">
-        <v>5.246808052062988</v>
+        <v>7.066723823547363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2282,7 +2282,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D99">
-        <v>8.325752258300781</v>
+        <v>9.615501403808594</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2296,7 +2296,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>2.911909580230713</v>
+        <v>2.958722591400146</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2310,7 +2310,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D101">
-        <v>5.666945457458496</v>
+        <v>5.332051277160645</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2324,7 +2324,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D102">
-        <v>0.8379571437835693</v>
+        <v>0.871329665184021</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2338,7 +2338,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D103">
-        <v>2.734070062637329</v>
+        <v>2.40394926071167</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D104">
-        <v>3.886866807937622</v>
+        <v>8.373703956604004</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D105">
-        <v>2.43506121635437</v>
+        <v>2.265324592590332</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2380,7 +2380,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D106">
-        <v>1.563069820404053</v>
+        <v>0.9527958631515503</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2394,7 +2394,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D107">
-        <v>7.986743927001953</v>
+        <v>8.931159973144531</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2408,7 +2408,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D108">
-        <v>1.445011258125305</v>
+        <v>1.113457679748535</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D109">
-        <v>2.84321928024292</v>
+        <v>1.843282103538513</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2436,7 +2436,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D110">
-        <v>2.47809362411499</v>
+        <v>2.975827217102051</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D111">
-        <v>4.096277236938477</v>
+        <v>5.142202377319336</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2464,7 +2464,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>1.077064633369446</v>
+        <v>1.189614772796631</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2478,7 +2478,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D113">
-        <v>2.264364242553711</v>
+        <v>2.468374252319336</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2492,7 +2492,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D114">
-        <v>6.456364631652832</v>
+        <v>5.307241439819336</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2506,7 +2506,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D115">
-        <v>2.693069696426392</v>
+        <v>2.978448867797852</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2520,7 +2520,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>1.465187788009644</v>
+        <v>1.790315985679626</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2534,7 +2534,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D117">
-        <v>2.531973838806152</v>
+        <v>2.368207931518555</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D118">
-        <v>2.989813804626465</v>
+        <v>3.88109302520752</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>5.5</v>
       </c>
       <c r="D119">
-        <v>3.138443470001221</v>
+        <v>3.925556659698486</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D120">
-        <v>2.264134883880615</v>
+        <v>1.533874273300171</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D121">
-        <v>2.176920890808105</v>
+        <v>1.699264049530029</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D122">
-        <v>2.883665323257446</v>
+        <v>4.127654552459717</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2618,7 +2618,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D123">
-        <v>1.644755959510803</v>
+        <v>2.550515174865723</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
       <c r="D124">
-        <v>3.642366647720337</v>
+        <v>4.255963802337646</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2646,7 +2646,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D125">
-        <v>2.161830902099609</v>
+        <v>1.784581542015076</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2660,7 +2660,7 @@
         <v>3.5</v>
       </c>
       <c r="D126">
-        <v>0.9007711410522461</v>
+        <v>1.099554419517517</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D127">
-        <v>9.808947563171387</v>
+        <v>9.976625442504883</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2688,7 +2688,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D128">
-        <v>0.8081985712051392</v>
+        <v>0.9442291259765625</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2702,7 +2702,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D129">
-        <v>3.15477442741394</v>
+        <v>4.209991455078125</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2716,7 +2716,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D130">
-        <v>1.11939001083374</v>
+        <v>1.067201256752014</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2730,7 +2730,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D131">
-        <v>1.172278642654419</v>
+        <v>1.389273166656494</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2744,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>3.494210481643677</v>
+        <v>2.90036678314209</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2758,7 +2758,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>1.487294435501099</v>
+        <v>1.056518316268921</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2772,7 +2772,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D134">
-        <v>1.507211446762085</v>
+        <v>2.583473205566406</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2786,7 +2786,7 @@
         <v>2.5</v>
       </c>
       <c r="D135">
-        <v>2.104346036911011</v>
+        <v>2.055902481079102</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2800,7 +2800,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D136">
-        <v>5.687307357788086</v>
+        <v>9.616094589233398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2814,7 +2814,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D137">
-        <v>1.81518030166626</v>
+        <v>1.0949547290802</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2828,7 +2828,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D138">
-        <v>2.894100666046143</v>
+        <v>2.806433200836182</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2842,7 +2842,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D139">
-        <v>2.826123237609863</v>
+        <v>2.528045654296875</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2856,7 +2856,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D140">
-        <v>5.433960914611816</v>
+        <v>5.811293125152588</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2870,7 +2870,7 @@
         <v>14.5</v>
       </c>
       <c r="D141">
-        <v>4.181838989257812</v>
+        <v>3.540557384490967</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2884,7 +2884,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D142">
-        <v>1.734072685241699</v>
+        <v>1.863423943519592</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2898,7 +2898,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D143">
-        <v>1.081344842910767</v>
+        <v>1.427741765975952</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2912,7 +2912,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D144">
-        <v>1.642250776290894</v>
+        <v>3.184725284576416</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2926,7 +2926,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D145">
-        <v>0.9960761070251465</v>
+        <v>1.354785919189453</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2940,7 +2940,7 @@
         <v>12</v>
       </c>
       <c r="D146">
-        <v>9.067534446716309</v>
+        <v>9.094409942626953</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -2954,7 +2954,7 @@
         <v>12.5</v>
       </c>
       <c r="D147">
-        <v>7.969409942626953</v>
+        <v>8.371047973632812</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2968,7 +2968,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D148">
-        <v>0.852596640586853</v>
+        <v>0.8432931900024414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0.8924624919891357</v>
+        <v>0.8804908990859985</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2996,7 +2996,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D150">
-        <v>1.431875467300415</v>
+        <v>1.019273519515991</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3010,7 +3010,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D151">
-        <v>1.288630485534668</v>
+        <v>1.24827241897583</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3024,7 +3024,7 @@
         <v>1.5</v>
       </c>
       <c r="D152">
-        <v>1.158258318901062</v>
+        <v>1.260241866111755</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3038,7 +3038,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D153">
-        <v>1.111565828323364</v>
+        <v>1.213625907897949</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3052,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="D154">
-        <v>2.746054649353027</v>
+        <v>3.300879001617432</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3066,7 +3066,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D155">
-        <v>4.843569755554199</v>
+        <v>4.056922912597656</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3080,7 +3080,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D156">
-        <v>2.465994596481323</v>
+        <v>1.566642761230469</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D157">
-        <v>0.8662509918212891</v>
+        <v>1.61742639541626</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3108,7 +3108,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D158">
-        <v>2.207197189331055</v>
+        <v>3.180544853210449</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3122,7 +3122,7 @@
         <v>9.5</v>
       </c>
       <c r="D159">
-        <v>4.747370719909668</v>
+        <v>5.126849174499512</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3136,7 +3136,7 @@
         <v>5.5</v>
       </c>
       <c r="D160">
-        <v>4.173402786254883</v>
+        <v>4.981711387634277</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3150,7 +3150,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.332631826400757</v>
+        <v>2.33982515335083</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3164,7 +3164,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D162">
-        <v>2.219796657562256</v>
+        <v>2.028223037719727</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3178,7 +3178,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D163">
-        <v>0.9596343040466309</v>
+        <v>1.236950397491455</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3192,7 +3192,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D164">
-        <v>1.170753955841064</v>
+        <v>1.182551980018616</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3206,7 +3206,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D165">
-        <v>1.460980415344238</v>
+        <v>1.186823129653931</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3220,7 +3220,7 @@
         <v>3</v>
       </c>
       <c r="D166">
-        <v>3.166199445724487</v>
+        <v>2.997066974639893</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3234,7 +3234,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D167">
-        <v>4.980759620666504</v>
+        <v>4.868180751800537</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3248,7 +3248,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D168">
-        <v>2.414097547531128</v>
+        <v>2.71380615234375</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3262,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>2.159830570220947</v>
+        <v>2.100517749786377</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3276,7 +3276,7 @@
         <v>5</v>
       </c>
       <c r="D170">
-        <v>1.422558188438416</v>
+        <v>2.285993576049805</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3290,7 +3290,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D171">
-        <v>1.208784461021423</v>
+        <v>1.170279026031494</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3304,7 +3304,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D172">
-        <v>3.858930349349976</v>
+        <v>3.738976955413818</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3318,7 +3318,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D173">
-        <v>1.212294459342957</v>
+        <v>2.279741287231445</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3332,7 +3332,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D174">
-        <v>2.265225648880005</v>
+        <v>7.226663112640381</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3346,7 +3346,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D175">
-        <v>0.9962266683578491</v>
+        <v>0.8762576580047607</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3360,7 +3360,7 @@
         <v>1.5</v>
       </c>
       <c r="D176">
-        <v>0.8982820510864258</v>
+        <v>0.8799554705619812</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3374,7 +3374,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D177">
-        <v>1.442492604255676</v>
+        <v>0.9616239070892334</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3388,7 +3388,7 @@
         <v>3.5</v>
       </c>
       <c r="D178">
-        <v>0.9334065914154053</v>
+        <v>1.046470403671265</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3402,7 +3402,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D179">
-        <v>1.14995265007019</v>
+        <v>1.381173491477966</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3416,7 +3416,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D180">
-        <v>1.185778856277466</v>
+        <v>1.018093824386597</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3430,7 +3430,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D181">
-        <v>1.708061218261719</v>
+        <v>1.984336495399475</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3444,7 +3444,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D182">
-        <v>3.981730937957764</v>
+        <v>3.878307342529297</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3458,7 +3458,7 @@
         <v>1.5</v>
       </c>
       <c r="D183">
-        <v>2.146432161331177</v>
+        <v>1.230472326278687</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3472,7 +3472,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D184">
-        <v>6.822859764099121</v>
+        <v>6.261106014251709</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3486,7 +3486,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D185">
-        <v>0.9288614988327026</v>
+        <v>1.304332494735718</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3500,7 +3500,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D186">
-        <v>1.566648840904236</v>
+        <v>2.418684005737305</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3514,7 +3514,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D187">
-        <v>0.9564405679702759</v>
+        <v>1.057531833648682</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3528,7 +3528,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D188">
-        <v>2.84917426109314</v>
+        <v>2.597375154495239</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3542,7 +3542,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D189">
-        <v>3.131421327590942</v>
+        <v>3.125349044799805</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3556,7 +3556,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D190">
-        <v>1.689618110656738</v>
+        <v>1.684491872787476</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3570,7 +3570,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D191">
-        <v>2.34723687171936</v>
+        <v>1.826806783676147</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3584,7 +3584,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D192">
-        <v>5.622687339782715</v>
+        <v>4.872562408447266</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3598,7 +3598,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D193">
-        <v>2.918611526489258</v>
+        <v>2.094549179077148</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3612,7 +3612,7 @@
         <v>2.5</v>
       </c>
       <c r="D194">
-        <v>1.37010931968689</v>
+        <v>1.052359700202942</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3626,7 +3626,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D195">
-        <v>1.341186285018921</v>
+        <v>1.22277307510376</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3640,7 +3640,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D196">
-        <v>2.285243511199951</v>
+        <v>2.57901406288147</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3654,7 +3654,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D197">
-        <v>3.041044473648071</v>
+        <v>3.125247955322266</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3668,7 +3668,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D198">
-        <v>2.205811500549316</v>
+        <v>1.810273289680481</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3682,7 +3682,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D199">
-        <v>4.220785140991211</v>
+        <v>4.105020046234131</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3696,7 +3696,7 @@
         <v>2.5</v>
       </c>
       <c r="D200">
-        <v>2.180661916732788</v>
+        <v>2.737650871276855</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3710,7 +3710,7 @@
         <v>2.5</v>
       </c>
       <c r="D201">
-        <v>5.005891799926758</v>
+        <v>3.59364128112793</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3724,7 +3724,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D202">
-        <v>2.438574552536011</v>
+        <v>8.158099174499512</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3738,7 +3738,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D203">
-        <v>1.069600462913513</v>
+        <v>1.431065082550049</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3752,7 +3752,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D204">
-        <v>0.891170859336853</v>
+        <v>0.8901738524436951</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3766,7 +3766,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D205">
-        <v>0.8840421438217163</v>
+        <v>0.9215868711471558</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3780,7 +3780,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>5.77421760559082</v>
+        <v>3.976132392883301</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3794,7 +3794,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D207">
-        <v>1.252650260925293</v>
+        <v>5.020390510559082</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3808,7 +3808,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D208">
-        <v>2.005824565887451</v>
+        <v>1.202461123466492</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3822,7 +3822,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D209">
-        <v>7.833528518676758</v>
+        <v>6.841477394104004</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3836,7 +3836,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D210">
-        <v>2.97105598449707</v>
+        <v>1.648404121398926</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3850,7 +3850,7 @@
         <v>1.5</v>
       </c>
       <c r="D211">
-        <v>5.30986213684082</v>
+        <v>4.182971477508545</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3864,7 +3864,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D212">
-        <v>0.8560991883277893</v>
+        <v>0.8303388357162476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3878,7 +3878,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D213">
-        <v>3.449974775314331</v>
+        <v>4.937478065490723</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3892,7 +3892,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D214">
-        <v>1.191871523857117</v>
+        <v>1.037869930267334</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3906,7 +3906,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D215">
-        <v>1.593528985977173</v>
+        <v>2.00357985496521</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3920,7 +3920,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D216">
-        <v>0.8613911867141724</v>
+        <v>0.849362313747406</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3934,7 +3934,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D217">
-        <v>1.922366380691528</v>
+        <v>1.072042107582092</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -3948,7 +3948,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D218">
-        <v>1.29707932472229</v>
+        <v>1.876984119415283</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>2.5</v>
       </c>
       <c r="D219">
-        <v>3.134189367294312</v>
+        <v>2.951724052429199</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -3976,7 +3976,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D220">
-        <v>2.141637563705444</v>
+        <v>1.891013026237488</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -3990,7 +3990,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D221">
-        <v>1.196395516395569</v>
+        <v>0.995622992515564</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4004,7 +4004,7 @@
         <v>3.5</v>
       </c>
       <c r="D222">
-        <v>3.482037782669067</v>
+        <v>5.121800422668457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4018,7 +4018,7 @@
         <v>6</v>
       </c>
       <c r="D223">
-        <v>3.426005601882935</v>
+        <v>3.579116821289062</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4032,7 +4032,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D224">
-        <v>7.372212409973145</v>
+        <v>5.679131031036377</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4046,7 +4046,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D225">
-        <v>2.526607751846313</v>
+        <v>3.347355365753174</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4060,7 +4060,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D226">
-        <v>1.405931711196899</v>
+        <v>2.151054382324219</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4074,7 +4074,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D227">
-        <v>3.734421968460083</v>
+        <v>3.881063461303711</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4088,7 +4088,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D228">
-        <v>3.981235980987549</v>
+        <v>4.357897281646729</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4102,7 +4102,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D229">
-        <v>4.134500980377197</v>
+        <v>7.378334522247314</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4116,7 +4116,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D230">
-        <v>5.097066879272461</v>
+        <v>4.859682559967041</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4130,7 +4130,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D231">
-        <v>3.951828241348267</v>
+        <v>4.588687419891357</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4144,7 +4144,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D232">
-        <v>1.698423624038696</v>
+        <v>1.34776771068573</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4158,7 +4158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D233">
-        <v>1.578575372695923</v>
+        <v>2.246068954467773</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="D234">
-        <v>4.813446998596191</v>
+        <v>3.339290142059326</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4186,7 +4186,7 @@
         <v>4</v>
       </c>
       <c r="D235">
-        <v>1.874267339706421</v>
+        <v>1.460738778114319</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4200,7 +4200,7 @@
         <v>4</v>
       </c>
       <c r="D236">
-        <v>1.141804456710815</v>
+        <v>1.206188678741455</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4214,7 +4214,7 @@
         <v>8</v>
       </c>
       <c r="D237">
-        <v>3.394091844558716</v>
+        <v>1.475785136222839</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4228,7 +4228,7 @@
         <v>10</v>
       </c>
       <c r="D238">
-        <v>10.09279727935791</v>
+        <v>9.852478981018066</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4242,7 +4242,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D239">
-        <v>7.835156440734863</v>
+        <v>9.31796932220459</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4256,7 +4256,7 @@
         <v>19</v>
       </c>
       <c r="D240">
-        <v>14.57828426361084</v>
+        <v>14.14481925964355</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4270,7 +4270,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D241">
-        <v>0.8598589897155762</v>
+        <v>0.9288352727890015</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4284,7 +4284,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D242">
-        <v>2.220791339874268</v>
+        <v>1.432012915611267</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4298,7 +4298,7 @@
         <v>3</v>
       </c>
       <c r="D243">
-        <v>1.660844683647156</v>
+        <v>2.135316848754883</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4312,7 +4312,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D244">
-        <v>1.648093581199646</v>
+        <v>3.874269962310791</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4326,7 +4326,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D245">
-        <v>1.527772188186646</v>
+        <v>1.847997188568115</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4340,7 +4340,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D246">
-        <v>2.040221929550171</v>
+        <v>1.58712363243103</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4354,7 +4354,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D247">
-        <v>7.961919784545898</v>
+        <v>9.222517013549805</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4368,7 +4368,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D248">
-        <v>1.552403450012207</v>
+        <v>1.177198052406311</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4382,7 +4382,7 @@
         <v>8</v>
       </c>
       <c r="D249">
-        <v>3.397653579711914</v>
+        <v>2.903621196746826</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4396,7 +4396,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D250">
-        <v>10.11190700531006</v>
+        <v>9.986865043640137</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4410,7 +4410,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D251">
-        <v>3.983206987380981</v>
+        <v>4.780577659606934</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4424,7 +4424,7 @@
         <v>7</v>
       </c>
       <c r="D252">
-        <v>4.052754402160645</v>
+        <v>3.261703491210938</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4438,7 +4438,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D253">
-        <v>4.984362602233887</v>
+        <v>1.896984815597534</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4452,7 +4452,7 @@
         <v>0.5</v>
       </c>
       <c r="D254">
-        <v>1.142475843429565</v>
+        <v>1.033679723739624</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4466,7 +4466,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D255">
-        <v>1.074966073036194</v>
+        <v>0.9259224534034729</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4480,7 +4480,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D256">
-        <v>5.282010078430176</v>
+        <v>4.697912216186523</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4494,7 +4494,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D257">
-        <v>2.163819313049316</v>
+        <v>1.765572428703308</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4508,7 +4508,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D258">
-        <v>3.346305131912231</v>
+        <v>1.922683000564575</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4522,7 +4522,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D259">
-        <v>0.9670350551605225</v>
+        <v>0.9549793004989624</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4536,7 +4536,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D260">
-        <v>0.9694622159004211</v>
+        <v>0.9496481418609619</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4550,7 +4550,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D261">
-        <v>0.9089936017990112</v>
+        <v>0.8348619937896729</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4564,7 +4564,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D262">
-        <v>1.055378675460815</v>
+        <v>1.217982292175293</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D263">
-        <v>3.455355405807495</v>
+        <v>3.599632740020752</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4592,7 +4592,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D264">
-        <v>0.8939690589904785</v>
+        <v>0.8795641660690308</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4606,7 +4606,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D265">
-        <v>2.208384037017822</v>
+        <v>1.543841004371643</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4620,7 +4620,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D266">
-        <v>6.325401306152344</v>
+        <v>6.170048713684082</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4634,7 +4634,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D267">
-        <v>1.837985277175903</v>
+        <v>1.843096375465393</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4648,7 +4648,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D268">
-        <v>3.180357217788696</v>
+        <v>3.544001579284668</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4662,7 +4662,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D269">
-        <v>2.58655309677124</v>
+        <v>3.230894565582275</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4676,7 +4676,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D270">
-        <v>2.630617380142212</v>
+        <v>3.397087097167969</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4690,7 +4690,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D271">
-        <v>1.109602928161621</v>
+        <v>1.147395014762878</v>
       </c>
     </row>
   </sheetData>
